--- a/results/v4主力_20260615.xlsx
+++ b/results/v4主力_20260615.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
         <v>1802</v>
       </c>
       <c r="N2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -551,20 +551,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>台嘉碩</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>67.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>84.09999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -573,22 +577,22 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>63.7</v>
+        <v>31.6</v>
       </c>
       <c r="J3" t="n">
         <v>0.0199</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>-5152</v>
       </c>
       <c r="L3" t="n">
-        <v>6.12</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>8932</v>
+        <v>93240</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -599,24 +603,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>泰谷</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>66.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F4" t="n">
-        <v>62.4</v>
+        <v>63.7</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -625,22 +625,22 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>31.6</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0199</v>
+        <v>0.0416</v>
       </c>
       <c r="K4" t="n">
-        <v>-5152</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>5.89</v>
       </c>
       <c r="M4" t="n">
-        <v>93240</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -651,20 +651,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>65.7</v>
+        <v>61.6</v>
       </c>
       <c r="F5" t="n">
-        <v>63.3</v>
+        <v>79.3</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -673,22 +673,22 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>44.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0202</v>
+        <v>0.0212</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>6.24</v>
       </c>
       <c r="M5" t="n">
-        <v>3980</v>
+        <v>1160</v>
       </c>
       <c r="N5" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -699,20 +699,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="F6" t="n">
-        <v>79.3</v>
+        <v>71.5</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -721,22 +721,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>64.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0212</v>
+        <v>-0.006</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>6.24</v>
+        <v>6.89</v>
       </c>
       <c r="M6" t="n">
-        <v>1160</v>
+        <v>929</v>
       </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -747,12 +747,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58.1</v>
+        <v>60.1</v>
       </c>
       <c r="F7" t="n">
-        <v>66.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -773,22 +773,22 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1570</v>
+        <v>141.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.042</v>
+        <v>0.0449</v>
       </c>
       <c r="K7" t="n">
-        <v>28.57</v>
+        <v>-3633</v>
       </c>
       <c r="L7" t="n">
-        <v>5.1</v>
+        <v>4.59</v>
       </c>
       <c r="M7" t="n">
-        <v>4977</v>
+        <v>126474</v>
       </c>
       <c r="N7" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -799,25 +799,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>威剛</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>映泰</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="F8" t="n">
         <v>53.6</v>
       </c>
-      <c r="F8" t="n">
-        <v>66.2</v>
-      </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
@@ -825,22 +821,22 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>423</v>
+        <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0222</v>
+        <v>0.0136</v>
       </c>
       <c r="K8" t="n">
-        <v>167</v>
+        <v>-47</v>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>2.92</v>
       </c>
       <c r="M8" t="n">
-        <v>-1503</v>
+        <v>-749</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -851,12 +847,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -865,10 +861,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>55.2</v>
       </c>
       <c r="F9" t="n">
-        <v>51.2</v>
+        <v>63.7</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -877,22 +873,22 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>159</v>
+        <v>590</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0307</v>
+        <v>0.0471</v>
       </c>
       <c r="K9" t="n">
-        <v>1487</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>5.66</v>
+        <v>5.93</v>
       </c>
       <c r="M9" t="n">
-        <v>27841</v>
+        <v>1454</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -903,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -917,34 +913,134 @@
         </is>
       </c>
       <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="K10" t="n">
+        <v>789</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1799</v>
+      </c>
+      <c r="N10" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="n">
         <v>51.2</v>
       </c>
-      <c r="F10" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="K10" t="n">
-        <v>166</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8831</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>159</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1487</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="M11" t="n">
+        <v>27841</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>新鉅科</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="M12" t="n">
+        <v>707</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -958,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,21 +1137,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>富喬</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>73.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1067,22 +1159,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>70.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0606</v>
+        <v>0.0198</v>
       </c>
       <c r="K2" t="n">
-        <v>-4083</v>
+        <v>1506</v>
       </c>
       <c r="L2" t="n">
-        <v>5.14</v>
+        <v>4.73</v>
       </c>
       <c r="M2" t="n">
-        <v>-16690</v>
+        <v>-16832</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -1134,7 +1226,7 @@
         <v>7675</v>
       </c>
       <c r="N3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -1145,21 +1237,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>光頡</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>70.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1171,22 +1259,22 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>117</v>
+        <v>129.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0188</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
-        <v>8.970000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="M4" t="n">
-        <v>85703</v>
+        <v>28536</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -1197,24 +1285,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>鈺創</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>67.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>43.3</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1223,22 +1307,22 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.25</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0122</v>
+        <v>0.0304</v>
       </c>
       <c r="K5" t="n">
-        <v>-4547</v>
+        <v>427</v>
       </c>
       <c r="L5" t="n">
-        <v>4.02</v>
+        <v>4.97</v>
       </c>
       <c r="M5" t="n">
-        <v>32352</v>
+        <v>-8485</v>
       </c>
       <c r="N5" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -1286,7 +1370,7 @@
         <v>12327</v>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -1297,20 +1381,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>63.4</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>28.6</v>
+        <v>35.2</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1319,22 +1403,22 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>145.5</v>
+        <v>176.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.034</v>
+        <v>0.0062</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="L7" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>11533</v>
+        <v>6955</v>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -1345,20 +1429,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>59.4</v>
       </c>
       <c r="F8" t="n">
-        <v>35.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1367,22 +1451,22 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>176.5</v>
+        <v>101</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0062</v>
+        <v>0.0348</v>
       </c>
       <c r="K8" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>5.74</v>
       </c>
       <c r="M8" t="n">
-        <v>6955</v>
+        <v>4668</v>
       </c>
       <c r="N8" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1393,20 +1477,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>61.6</v>
+        <v>57.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1415,22 +1499,22 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>55.3</v>
+        <v>544</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0219</v>
+        <v>0.0289</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="L9" t="n">
-        <v>7.05</v>
+        <v>6.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3835</v>
+        <v>-5216</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -1441,20 +1525,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>59.7</v>
+        <v>55.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1463,22 +1547,22 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>16.7</v>
+        <v>49</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0526</v>
+        <v>0.0154</v>
       </c>
       <c r="K10" t="n">
-        <v>-75</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>4.19</v>
+        <v>1.63</v>
       </c>
       <c r="M10" t="n">
-        <v>50754</v>
+        <v>-231</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -1489,20 +1573,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>美琪瑪</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>59.4</v>
+        <v>54.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1511,22 +1595,22 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>101</v>
+        <v>11.55</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0348</v>
+        <v>0.0177</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5.74</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="n">
-        <v>4668</v>
+        <v>-104</v>
       </c>
       <c r="N11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -1537,17 +1621,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>九豪</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>台灣高鐵</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>58.1</v>
+        <v>50.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1559,217 +1647,21 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>79</v>
+        <v>25.55</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0277</v>
+        <v>0.0098</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-371</v>
       </c>
       <c r="L12" t="n">
-        <v>2.53</v>
+        <v>0.78</v>
       </c>
       <c r="M12" t="n">
-        <v>3685</v>
+        <v>-2747</v>
       </c>
       <c r="N12" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B XGB獨立</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5483</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>中美晶</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>174.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K13" t="n">
-        <v>262</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="M13" t="n">
-        <v>27972</v>
-      </c>
-      <c r="N13" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B XGB獨立</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>6156</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>松上</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>48</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3711</v>
-      </c>
-      <c r="N14" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>B XGB獨立</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6126</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>信音</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>41.65</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.0161</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-209</v>
-      </c>
-      <c r="N15" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>B XGB獨立</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>6175</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>立敦</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>108</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="M16" t="n">
-        <v>12576</v>
-      </c>
-      <c r="N16" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1784,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,24 +1759,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>鈦昇</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F2" t="n">
-        <v>68.59999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1893,22 +1781,22 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>37.85</v>
+        <v>239</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0385</v>
+        <v>0.0108</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>147</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>5.44</v>
       </c>
       <c r="M2" t="n">
-        <v>-44871</v>
+        <v>-2452</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -1919,24 +1807,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>尚立</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>47.8</v>
+        <v>48.6</v>
       </c>
       <c r="F3" t="n">
-        <v>82.59999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1945,22 +1829,22 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>51.6</v>
+        <v>15.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0246</v>
+        <v>0.0333</v>
       </c>
       <c r="K3" t="n">
-        <v>-1048</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.65</v>
+        <v>2.96</v>
       </c>
       <c r="M3" t="n">
-        <v>21253</v>
+        <v>-193</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -1971,12 +1855,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1985,10 +1869,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="F4" t="n">
-        <v>54.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1997,22 +1881,22 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>189</v>
+        <v>51.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0436</v>
+        <v>0.0246</v>
       </c>
       <c r="K4" t="n">
-        <v>4823</v>
+        <v>-1048</v>
       </c>
       <c r="L4" t="n">
-        <v>7.41</v>
+        <v>4.65</v>
       </c>
       <c r="M4" t="n">
-        <v>229466</v>
+        <v>21253</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2023,20 +1907,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>茂矽</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>47.7</v>
       </c>
       <c r="F5" t="n">
-        <v>57.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2045,22 +1929,22 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>26.95</v>
+        <v>43.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0429</v>
+        <v>0.0244</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>-51</v>
       </c>
       <c r="L5" t="n">
-        <v>6.49</v>
+        <v>7.09</v>
       </c>
       <c r="M5" t="n">
-        <v>5059</v>
+        <v>3025</v>
       </c>
       <c r="N5" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -2071,20 +1955,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜鼎</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>44.2</v>
+        <v>47.3</v>
       </c>
       <c r="F6" t="n">
-        <v>63.2</v>
+        <v>54.3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2093,22 +1981,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1920</v>
+        <v>189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0249</v>
+        <v>0.0436</v>
       </c>
       <c r="K6" t="n">
-        <v>39</v>
+        <v>4823</v>
       </c>
       <c r="L6" t="n">
-        <v>5.47</v>
+        <v>7.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1618</v>
+        <v>229466</v>
       </c>
       <c r="N6" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2119,20 +2007,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>漢磊</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>43.8</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>82.09999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2141,22 +2029,22 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>81.7</v>
+        <v>26.95</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0506</v>
+        <v>0.0429</v>
       </c>
       <c r="K7" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>3.18</v>
+        <v>6.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-2291</v>
+        <v>5059</v>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -2167,20 +2055,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>40.5</v>
+        <v>44.2</v>
       </c>
       <c r="F8" t="n">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2189,19 +2077,19 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>31.9</v>
+        <v>1920</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0322</v>
+        <v>0.0249</v>
       </c>
       <c r="K8" t="n">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="L8" t="n">
-        <v>7.99</v>
+        <v>5.47</v>
       </c>
       <c r="M8" t="n">
-        <v>-11561</v>
+        <v>1618</v>
       </c>
       <c r="N8" t="n">
         <v>45</v>
@@ -2215,20 +2103,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>39.6</v>
+        <v>38.9</v>
       </c>
       <c r="F9" t="n">
-        <v>57.2</v>
+        <v>57.9</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2237,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>35.6</v>
+        <v>86.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0494</v>
+        <v>0.017</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L9" t="n">
-        <v>7.3</v>
+        <v>7.84</v>
       </c>
       <c r="M9" t="n">
-        <v>3015</v>
+        <v>3293</v>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2263,48 +2151,200 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>久陽</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>18</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M10" t="n">
+        <v>43</v>
+      </c>
+      <c r="N10" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C Tree獨立</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>台亞</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-357</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C Tree獨立</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2884</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>玉山金</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>25.3</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F12" t="n">
         <v>62.3</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
         <v>34.65</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>0.0146</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K12" t="n">
         <v>11142</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" t="n">
         <v>4592</v>
       </c>
-      <c r="N10" t="n">
-        <v>14</v>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C Tree獨立</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-3800</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M13" t="n">
+        <v>71719</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2318,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2442,7 +2482,7 @@
         <v>1802</v>
       </c>
       <c r="N2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -2453,20 +2493,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>台嘉碩</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>67.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>84.09999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -2475,22 +2519,22 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>63.7</v>
+        <v>31.6</v>
       </c>
       <c r="J3" t="n">
         <v>0.0199</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>-5152</v>
       </c>
       <c r="L3" t="n">
-        <v>6.12</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>8932</v>
+        <v>93240</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2501,24 +2545,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>泰谷</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>66.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F4" t="n">
-        <v>62.4</v>
+        <v>63.7</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -2527,22 +2567,22 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>31.6</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0199</v>
+        <v>0.0416</v>
       </c>
       <c r="K4" t="n">
-        <v>-5152</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>5.89</v>
       </c>
       <c r="M4" t="n">
-        <v>93240</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -2553,20 +2593,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>65.7</v>
+        <v>61.6</v>
       </c>
       <c r="F5" t="n">
-        <v>63.3</v>
+        <v>79.3</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -2575,22 +2615,22 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>44.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0202</v>
+        <v>0.0212</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>6.24</v>
       </c>
       <c r="M5" t="n">
-        <v>3980</v>
+        <v>1160</v>
       </c>
       <c r="N5" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -2601,20 +2641,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="F6" t="n">
-        <v>79.3</v>
+        <v>71.5</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -2623,22 +2663,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>64.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0212</v>
+        <v>-0.006</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>6.24</v>
+        <v>6.89</v>
       </c>
       <c r="M6" t="n">
-        <v>1160</v>
+        <v>929</v>
       </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -2649,12 +2689,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2663,10 +2703,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58.1</v>
+        <v>60.1</v>
       </c>
       <c r="F7" t="n">
-        <v>66.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -2675,22 +2715,22 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1570</v>
+        <v>141.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.042</v>
+        <v>0.0449</v>
       </c>
       <c r="K7" t="n">
-        <v>28.57</v>
+        <v>-3633</v>
       </c>
       <c r="L7" t="n">
-        <v>5.1</v>
+        <v>4.59</v>
       </c>
       <c r="M7" t="n">
-        <v>4977</v>
+        <v>126474</v>
       </c>
       <c r="N7" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2701,25 +2741,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>威剛</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>映泰</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="F8" t="n">
         <v>53.6</v>
       </c>
-      <c r="F8" t="n">
-        <v>66.2</v>
-      </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
@@ -2727,22 +2763,22 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>423</v>
+        <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0222</v>
+        <v>0.0136</v>
       </c>
       <c r="K8" t="n">
-        <v>167</v>
+        <v>-47</v>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>2.92</v>
       </c>
       <c r="M8" t="n">
-        <v>-1503</v>
+        <v>-749</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2753,12 +2789,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2767,10 +2803,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>55.2</v>
       </c>
       <c r="F9" t="n">
-        <v>51.2</v>
+        <v>63.7</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -2779,22 +2815,22 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>159</v>
+        <v>590</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0307</v>
+        <v>0.0471</v>
       </c>
       <c r="K9" t="n">
-        <v>1487</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>5.66</v>
+        <v>5.93</v>
       </c>
       <c r="M9" t="n">
-        <v>27841</v>
+        <v>1454</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -2805,12 +2841,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2819,10 +2855,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>51.2</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>86.8</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -2831,38 +2867,38 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>38.45</v>
+        <v>428.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0286</v>
+        <v>0.0263</v>
       </c>
       <c r="K10" t="n">
-        <v>166</v>
+        <v>789</v>
       </c>
       <c r="L10" t="n">
-        <v>5.72</v>
+        <v>4.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8831</v>
+        <v>-1799</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B XGB獨立</t>
+          <t>A 強訊號</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2871,86 +2907,82 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>73.7</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>70.09999999999999</v>
+        <v>159</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0606</v>
+        <v>0.0307</v>
       </c>
       <c r="K11" t="n">
-        <v>-4083</v>
+        <v>1487</v>
       </c>
       <c r="L11" t="n">
-        <v>5.14</v>
+        <v>5.66</v>
       </c>
       <c r="M11" t="n">
-        <v>-16690</v>
+        <v>27841</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B XGB獨立</t>
+          <t>A 強訊號</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合晶</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>新鉅科</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>71.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>74.7</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>97.7</v>
+        <v>30.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0596</v>
+        <v>0.0052</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>6.89</v>
       </c>
       <c r="M12" t="n">
-        <v>7675</v>
+        <v>707</v>
       </c>
       <c r="N12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -2961,21 +2993,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>富喬</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>70.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2987,22 +3015,22 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>117</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0188</v>
+        <v>0.0198</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>1506</v>
       </c>
       <c r="L13" t="n">
-        <v>8.970000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="M13" t="n">
-        <v>85703</v>
+        <v>-16832</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3013,12 +3041,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3027,7 +3055,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3039,22 +3067,22 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>47.25</v>
+        <v>97.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0122</v>
+        <v>0.0596</v>
       </c>
       <c r="K14" t="n">
-        <v>-4547</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="M14" t="n">
-        <v>32352</v>
+        <v>7675</v>
       </c>
       <c r="N14" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -3065,17 +3093,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>光頡</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>66.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3087,22 +3115,22 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>202.5</v>
+        <v>129.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>5.68</v>
+        <v>9.65</v>
       </c>
       <c r="M15" t="n">
-        <v>12327</v>
+        <v>28536</v>
       </c>
       <c r="N15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3113,20 +3141,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>63.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>28.6</v>
+        <v>43.3</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -3135,22 +3163,22 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>145.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.034</v>
+        <v>0.0304</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>427</v>
       </c>
       <c r="L16" t="n">
-        <v>8.25</v>
+        <v>4.97</v>
       </c>
       <c r="M16" t="n">
-        <v>11533</v>
+        <v>-8485</v>
       </c>
       <c r="N16" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -3161,20 +3189,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>35.2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -3183,22 +3211,22 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>176.5</v>
+        <v>202.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0062</v>
+        <v>0.0352</v>
       </c>
       <c r="K17" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>5.68</v>
       </c>
       <c r="M17" t="n">
-        <v>6955</v>
+        <v>12327</v>
       </c>
       <c r="N17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -3209,20 +3237,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>61.6</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -3231,22 +3259,22 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>55.3</v>
+        <v>176.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0219</v>
+        <v>0.0062</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L18" t="n">
-        <v>7.05</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3835</v>
+        <v>6955</v>
       </c>
       <c r="N18" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -3257,17 +3285,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>59.7</v>
+        <v>59.4</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -3279,22 +3307,22 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>16.7</v>
+        <v>101</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0526</v>
+        <v>0.0348</v>
       </c>
       <c r="K19" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4.19</v>
+        <v>5.74</v>
       </c>
       <c r="M19" t="n">
-        <v>50754</v>
+        <v>4668</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3305,20 +3333,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>美琪瑪</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>59.4</v>
+        <v>57.7</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -3327,22 +3355,22 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>101</v>
+        <v>544</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0348</v>
+        <v>0.0289</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="L20" t="n">
-        <v>5.74</v>
+        <v>6.25</v>
       </c>
       <c r="M20" t="n">
-        <v>4668</v>
+        <v>-5216</v>
       </c>
       <c r="N20" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
@@ -3353,20 +3381,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>九豪</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>58.1</v>
+        <v>55.8</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -3375,22 +3403,22 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0277</v>
+        <v>0.0154</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2.53</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3685</v>
+        <v>-231</v>
       </c>
       <c r="N21" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -3401,24 +3429,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中美晶</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>太欣</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>57.3</v>
+        <v>54.8</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -3427,22 +3451,22 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>174.5</v>
+        <v>11.55</v>
       </c>
       <c r="J22" t="n">
-        <v>0.044</v>
+        <v>0.0177</v>
       </c>
       <c r="K22" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>5.73</v>
+        <v>3.9</v>
       </c>
       <c r="M22" t="n">
-        <v>27972</v>
+        <v>-104</v>
       </c>
       <c r="N22" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -3453,20 +3477,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>松上</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>台灣高鐵</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>55.1</v>
+        <v>50.4</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -3475,118 +3503,118 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>22.6</v>
+        <v>25.55</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-371</v>
       </c>
       <c r="L23" t="n">
-        <v>13.72</v>
+        <v>0.78</v>
       </c>
       <c r="M23" t="n">
-        <v>3711</v>
+        <v>-2747</v>
       </c>
       <c r="N23" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B XGB獨立</t>
+          <t>C Tree獨立</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>信音</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>51.8</v>
+        <v>49.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>51.7</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>41.65</v>
+        <v>239</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0161</v>
+        <v>0.0108</v>
       </c>
       <c r="K24" t="n">
-        <v>-6</v>
+        <v>147</v>
       </c>
       <c r="L24" t="n">
-        <v>7.68</v>
+        <v>5.44</v>
       </c>
       <c r="M24" t="n">
-        <v>-209</v>
+        <v>-2452</v>
       </c>
       <c r="N24" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B XGB獨立</t>
+          <t>C Tree獨立</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>尚立</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>51.1</v>
+        <v>48.6</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>108</v>
+        <v>15.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0294</v>
+        <v>0.0333</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>-0</v>
       </c>
       <c r="L25" t="n">
-        <v>6.02</v>
+        <v>2.96</v>
       </c>
       <c r="M25" t="n">
-        <v>12576</v>
+        <v>-193</v>
       </c>
       <c r="N25" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
@@ -3597,12 +3625,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3611,10 +3639,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49.2</v>
+        <v>47.8</v>
       </c>
       <c r="F26" t="n">
-        <v>68.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -3623,22 +3651,22 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>37.85</v>
+        <v>51.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0385</v>
+        <v>0.0246</v>
       </c>
       <c r="K26" t="n">
-        <v>-0</v>
+        <v>-1048</v>
       </c>
       <c r="L26" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="M26" t="n">
-        <v>-44871</v>
+        <v>21253</v>
       </c>
       <c r="N26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -3649,24 +3677,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>茂矽</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="F27" t="n">
-        <v>82.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -3675,19 +3699,19 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>51.6</v>
+        <v>43.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0246</v>
+        <v>0.0244</v>
       </c>
       <c r="K27" t="n">
-        <v>-1048</v>
+        <v>-51</v>
       </c>
       <c r="L27" t="n">
-        <v>4.65</v>
+        <v>7.09</v>
       </c>
       <c r="M27" t="n">
-        <v>21253</v>
+        <v>3025</v>
       </c>
       <c r="N27" t="n">
         <v>19</v>
@@ -3742,7 +3766,7 @@
         <v>229466</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -3790,7 +3814,7 @@
         <v>5059</v>
       </c>
       <c r="N29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
@@ -3838,7 +3862,7 @@
         <v>1618</v>
       </c>
       <c r="N30" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
@@ -3849,20 +3873,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>漢磊</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>43.8</v>
+        <v>38.9</v>
       </c>
       <c r="F31" t="n">
-        <v>82.09999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3871,22 +3895,22 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>81.7</v>
+        <v>86.7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0506</v>
+        <v>0.017</v>
       </c>
       <c r="K31" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L31" t="n">
-        <v>3.18</v>
+        <v>7.84</v>
       </c>
       <c r="M31" t="n">
-        <v>-2291</v>
+        <v>3293</v>
       </c>
       <c r="N31" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -3897,20 +3921,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>久陽</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>40.5</v>
+        <v>35.1</v>
       </c>
       <c r="F32" t="n">
-        <v>66.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3919,22 +3943,22 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>31.9</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0322</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>7.99</v>
+        <v>2.78</v>
       </c>
       <c r="M32" t="n">
-        <v>-11561</v>
+        <v>43</v>
       </c>
       <c r="N32" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
@@ -3945,20 +3969,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>振發</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>台亞</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>39.6</v>
+        <v>30.9</v>
       </c>
       <c r="F33" t="n">
-        <v>57.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3967,22 +3995,22 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>35.6</v>
+        <v>36.6</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0494</v>
+        <v>0.026</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>-357</v>
       </c>
       <c r="L33" t="n">
-        <v>7.3</v>
+        <v>5.46</v>
       </c>
       <c r="M33" t="n">
-        <v>3015</v>
+        <v>2012</v>
       </c>
       <c r="N33" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -4034,55 +4062,59 @@
         <v>4592</v>
       </c>
       <c r="N34" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>D 無訊號</t>
+          <t>C Tree獨立</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>雷科</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>49.9</v>
+        <v>23.3</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>136</v>
+        <v>395.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0565</v>
+        <v>0.0455</v>
       </c>
       <c r="K35" t="n">
-        <v>-0</v>
+        <v>-3800</v>
       </c>
       <c r="L35" t="n">
-        <v>3.68</v>
+        <v>4.42</v>
       </c>
       <c r="M35" t="n">
-        <v>7627</v>
+        <v>71719</v>
       </c>
       <c r="N35" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -4093,24 +4125,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>智原</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>雷科</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -4119,22 +4147,22 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0353</v>
+        <v>0.0565</v>
       </c>
       <c r="K36" t="n">
-        <v>-483</v>
+        <v>-0</v>
       </c>
       <c r="L36" t="n">
-        <v>5.94</v>
+        <v>3.68</v>
       </c>
       <c r="M36" t="n">
-        <v>13752</v>
+        <v>7627</v>
       </c>
       <c r="N36" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -4145,24 +4173,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>福裕</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>48.9</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>43.1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -4171,22 +4195,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>21.4</v>
+        <v>15.75</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0466</v>
+        <v>0.0032</v>
       </c>
       <c r="K37" t="n">
-        <v>-2549</v>
+        <v>-0</v>
       </c>
       <c r="L37" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="M37" t="n">
-        <v>17161</v>
+        <v>191</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
@@ -4197,20 +4221,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>華紙</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F38" t="n">
-        <v>41.1</v>
+        <v>44.2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -4219,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>145.5</v>
+        <v>12.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0212</v>
+        <v>0.0116</v>
       </c>
       <c r="K38" t="n">
-        <v>110</v>
+        <v>-278</v>
       </c>
       <c r="L38" t="n">
-        <v>4.81</v>
+        <v>2.71</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>-1852</v>
       </c>
       <c r="N38" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
@@ -4245,12 +4273,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4259,10 +4287,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>47.6</v>
+        <v>44.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>46.9</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -4271,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>940</v>
+        <v>369</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0772</v>
+        <v>0.054</v>
       </c>
       <c r="K39" t="n">
-        <v>494</v>
+        <v>95</v>
       </c>
       <c r="L39" t="n">
-        <v>2.02</v>
+        <v>5.01</v>
       </c>
       <c r="M39" t="n">
-        <v>42100</v>
+        <v>8174</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
@@ -4297,12 +4325,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4311,7 +4339,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>47.1</v>
+        <v>43.1</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -4323,22 +4351,22 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0206</v>
+        <v>0.0072</v>
       </c>
       <c r="K40" t="n">
-        <v>41</v>
+        <v>383</v>
       </c>
       <c r="L40" t="n">
-        <v>7.59</v>
+        <v>7.03</v>
       </c>
       <c r="M40" t="n">
-        <v>11162</v>
+        <v>-53146</v>
       </c>
       <c r="N40" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -4349,12 +4377,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4363,7 +4391,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>46.8</v>
+        <v>42.7</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -4375,22 +4403,22 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>31.45</v>
+        <v>104</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0227</v>
+        <v>0.0448</v>
       </c>
       <c r="K41" t="n">
-        <v>118</v>
+        <v>1517</v>
       </c>
       <c r="L41" t="n">
-        <v>8.27</v>
+        <v>2.4</v>
       </c>
       <c r="M41" t="n">
-        <v>29203</v>
+        <v>-5075</v>
       </c>
       <c r="N41" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -4401,17 +4429,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>風青</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -4423,22 +4451,22 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>322</v>
+        <v>39.75</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0307</v>
+        <v>0.0775</v>
       </c>
       <c r="K42" t="n">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="L42" t="n">
-        <v>6.37</v>
+        <v>2.01</v>
       </c>
       <c r="M42" t="n">
-        <v>14143</v>
+        <v>801</v>
       </c>
       <c r="N42" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43">
@@ -4449,24 +4477,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>世界</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>橘子</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -4475,22 +4499,22 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>174.5</v>
+        <v>43.95</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0295</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="L43" t="n">
-        <v>3.44</v>
+        <v>1.82</v>
       </c>
       <c r="M43" t="n">
-        <v>9209</v>
+        <v>-614</v>
       </c>
       <c r="N43" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -4501,20 +4525,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>宇峻</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>39.9</v>
+        <v>41.3</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -4523,22 +4547,22 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>76.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0101</v>
+        <v>0.0122</v>
       </c>
       <c r="K44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L44" t="n">
-        <v>8.140000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="M44" t="n">
-        <v>2412</v>
+        <v>-250</v>
       </c>
       <c r="N44" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
@@ -4549,24 +4573,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>海德威</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>39.2</v>
+        <v>41.1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4575,22 +4595,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2375</v>
+        <v>19.65</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0216</v>
+        <v>0.0301</v>
       </c>
       <c r="K45" t="n">
-        <v>-8345</v>
+        <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="M45" t="n">
-        <v>30228</v>
+        <v>-148</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46">
@@ -4601,17 +4621,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>37.6</v>
+        <v>40.6</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -4623,22 +4647,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>29.9</v>
+        <v>174.5</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0104</v>
+        <v>0.0295</v>
       </c>
       <c r="K46" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>5.02</v>
+        <v>3.44</v>
       </c>
       <c r="M46" t="n">
-        <v>984</v>
+        <v>9209</v>
       </c>
       <c r="N46" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
@@ -4649,24 +4673,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>聯一光</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>33.8</v>
+        <v>40</v>
       </c>
       <c r="F47" t="n">
-        <v>24.4</v>
+        <v>43.7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -4675,22 +4695,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>28.8</v>
+        <v>73.7</v>
       </c>
       <c r="J47" t="n">
-        <v>0.031</v>
+        <v>0.02</v>
       </c>
       <c r="K47" t="n">
-        <v>-6763</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="M47" t="n">
-        <v>81696</v>
+        <v>631</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
@@ -4701,20 +4721,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>劍湖山</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>33.3</v>
+        <v>39.6</v>
       </c>
       <c r="F48" t="n">
-        <v>34.9</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -4723,22 +4743,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>102.5</v>
+        <v>5.01</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0202</v>
+        <v>-0.075</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.93</v>
+        <v>10.78</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="N48" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49">
@@ -4749,20 +4769,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>亞矽</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>32.7</v>
+        <v>38.7</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -4771,22 +4791,22 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>48.8</v>
+        <v>27.45</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0327</v>
+        <v>0.0055</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L49" t="n">
-        <v>6.76</v>
+        <v>2.37</v>
       </c>
       <c r="M49" t="n">
-        <v>6934</v>
+        <v>241</v>
       </c>
       <c r="N49" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50">
@@ -4797,20 +4817,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>慶騰</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E50" t="n">
-        <v>32.1</v>
+        <v>38.5</v>
       </c>
       <c r="F50" t="n">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -4819,22 +4843,22 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>35.6</v>
+        <v>44</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0591</v>
+        <v>0.0357</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-39.01</v>
       </c>
       <c r="L50" t="n">
-        <v>3.79</v>
+        <v>3.52</v>
       </c>
       <c r="M50" t="n">
-        <v>-240</v>
+        <v>-6805</v>
       </c>
       <c r="N50" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -4845,17 +4869,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>華容</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E51" t="n">
-        <v>30.8</v>
+        <v>37.7</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -4867,22 +4895,22 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>46.55</v>
+        <v>950</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0272</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="L51" t="n">
-        <v>6.55</v>
+        <v>3.37</v>
       </c>
       <c r="M51" t="n">
-        <v>26338</v>
+        <v>5061</v>
       </c>
       <c r="N51" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
@@ -4893,24 +4921,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>宜特</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>28.9</v>
+        <v>36.3</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -4919,22 +4943,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>67.40000000000001</v>
+        <v>169</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0296</v>
+        <v>0.0533</v>
       </c>
       <c r="K52" t="n">
-        <v>-1255</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>6.53</v>
+        <v>2.66</v>
       </c>
       <c r="M52" t="n">
-        <v>22615</v>
+        <v>1083</v>
       </c>
       <c r="N52" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53">
@@ -4945,20 +4969,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>國統</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>瑞軒</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E53" t="n">
-        <v>28.7</v>
+        <v>34</v>
       </c>
       <c r="F53" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -4967,22 +4995,22 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>57.9</v>
+        <v>45</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0161</v>
+        <v>0.0252</v>
       </c>
       <c r="K53" t="n">
-        <v>125</v>
+        <v>-2278</v>
       </c>
       <c r="L53" t="n">
-        <v>6.39</v>
+        <v>7.44</v>
       </c>
       <c r="M53" t="n">
-        <v>1919</v>
+        <v>12346</v>
       </c>
       <c r="N53" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
@@ -4993,20 +5021,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>佶優</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E54" t="n">
-        <v>28.6</v>
+        <v>33.8</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -5015,22 +5047,22 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>33.45</v>
+        <v>28.8</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0342</v>
+        <v>0.031</v>
       </c>
       <c r="K54" t="n">
-        <v>68</v>
+        <v>-6763</v>
       </c>
       <c r="L54" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="M54" t="n">
-        <v>880</v>
+        <v>81696</v>
       </c>
       <c r="N54" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -5041,20 +5073,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>28.1</v>
+        <v>30.8</v>
       </c>
       <c r="F55" t="n">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -5063,22 +5095,22 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>39.4</v>
+        <v>46.55</v>
       </c>
       <c r="J55" t="n">
-        <v>0.046</v>
+        <v>0.0272</v>
       </c>
       <c r="K55" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>4.82</v>
+        <v>6.55</v>
       </c>
       <c r="M55" t="n">
-        <v>2387</v>
+        <v>26338</v>
       </c>
       <c r="N55" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -5089,24 +5121,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>亞通</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>27.9</v>
+        <v>29.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -5115,22 +5143,22 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0358</v>
+        <v>0.0042</v>
       </c>
       <c r="K56" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>4.88</v>
+        <v>1.25</v>
       </c>
       <c r="M56" t="n">
-        <v>21099</v>
+        <v>-580</v>
       </c>
       <c r="N56" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
@@ -5141,21 +5169,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>崧騰</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -5167,22 +5191,22 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>243.5</v>
+        <v>47</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0312</v>
+        <v>0.0055</v>
       </c>
       <c r="K57" t="n">
-        <v>-1736</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>6.37</v>
+        <v>3.62</v>
       </c>
       <c r="M57" t="n">
-        <v>29915</v>
+        <v>219</v>
       </c>
       <c r="N57" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58">
@@ -5193,12 +5217,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5207,7 +5231,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -5219,22 +5243,22 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>35.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0249</v>
+        <v>0.0296</v>
       </c>
       <c r="K58" t="n">
-        <v>-6236</v>
+        <v>-1255</v>
       </c>
       <c r="L58" t="n">
-        <v>2.84</v>
+        <v>6.53</v>
       </c>
       <c r="M58" t="n">
-        <v>55676</v>
+        <v>22615</v>
       </c>
       <c r="N58" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -5245,20 +5269,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>24.3</v>
+        <v>28.6</v>
       </c>
       <c r="F59" t="n">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -5267,22 +5291,22 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>103</v>
+        <v>33.45</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0235</v>
+        <v>0.0342</v>
       </c>
       <c r="K59" t="n">
-        <v>415</v>
+        <v>68</v>
       </c>
       <c r="L59" t="n">
-        <v>8.35</v>
+        <v>2.69</v>
       </c>
       <c r="M59" t="n">
-        <v>21332</v>
+        <v>880</v>
       </c>
       <c r="N59" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
@@ -5293,12 +5317,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5307,10 +5331,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>17.8</v>
+        <v>27.9</v>
       </c>
       <c r="F60" t="n">
-        <v>6.3</v>
+        <v>43.3</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -5319,22 +5343,22 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>39.95</v>
+        <v>51.4</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0336</v>
+        <v>0.0505</v>
       </c>
       <c r="K60" t="n">
-        <v>-6449</v>
+        <v>110668</v>
       </c>
       <c r="L60" t="n">
-        <v>2.63</v>
+        <v>3.31</v>
       </c>
       <c r="M60" t="n">
-        <v>3731</v>
+        <v>88275</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
@@ -5345,12 +5369,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5359,7 +5383,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>15.1</v>
+        <v>24.4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -5371,22 +5395,22 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>127.5</v>
+        <v>36.7</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0328</v>
+        <v>0.0417</v>
       </c>
       <c r="K61" t="n">
-        <v>1576.35</v>
+        <v>-4458</v>
       </c>
       <c r="L61" t="n">
-        <v>2.75</v>
+        <v>3.81</v>
       </c>
       <c r="M61" t="n">
-        <v>18491</v>
+        <v>-2708</v>
       </c>
       <c r="N61" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
@@ -5397,21 +5421,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>遠東新</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>遠東銀</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>11.9</v>
+        <v>22.8</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -5423,22 +5443,22 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>27.55</v>
+        <v>12.85</v>
       </c>
       <c r="J62" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0077</v>
       </c>
       <c r="K62" t="n">
-        <v>268</v>
+        <v>-292</v>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="M62" t="n">
-        <v>14966</v>
+        <v>-7969</v>
       </c>
       <c r="N62" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -5449,48 +5469,408 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>22</v>
+      </c>
+      <c r="F63" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>751</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="K63" t="n">
+        <v>582</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-935</v>
+      </c>
+      <c r="N63" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="K64" t="n">
+        <v>526</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-28708</v>
+      </c>
+      <c r="N64" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-6449</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3731</v>
+      </c>
+      <c r="N65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1576.35</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M66" t="n">
+        <v>18491</v>
+      </c>
+      <c r="N66" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>268</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M67" t="n">
+        <v>14966</v>
+      </c>
+      <c r="N67" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-2201</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-3059</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>7777</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>能率亞洲</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="K69" t="n">
+        <v>33</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-3191</v>
+      </c>
+      <c r="N69" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>2892</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>第一金</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E70" t="n">
         <v>5.4</v>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
         <v>31.3</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J70" t="n">
         <v>0.0113</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K70" t="n">
         <v>-5112</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L70" t="n">
         <v>1.92</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M70" t="n">
         <v>-6529</v>
       </c>
-      <c r="N63" t="n">
-        <v>15</v>
+      <c r="N70" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
